--- a/Format Rekap SKP per OPD.xlsx
+++ b/Format Rekap SKP per OPD.xlsx
@@ -1,101 +1,53 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\aplikasi firas\Dashboard Penilaian\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DF55C17-F6ED-470A-B9F8-823E36DA550F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D53DF79B-7FBF-4364-855C-CA4278B4004D}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet3" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet3!$A$4:$I$4</definedName>
-  </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t>NIP</t>
-  </si>
-  <si>
-    <t>NAMA</t>
-  </si>
-  <si>
-    <t>GOL. RUANG</t>
-  </si>
-  <si>
-    <t>JABATAN</t>
-  </si>
-  <si>
-    <t>SATUAN KERJA</t>
-  </si>
-  <si>
-    <t>JENIS ASN</t>
-  </si>
-  <si>
-    <t>NILAI SKP</t>
-  </si>
-  <si>
-    <t>KET</t>
-  </si>
-  <si>
-    <t>LAPORAN HASIL PENILAIAN KINERJA (SKP) ASN JULI TAHUN 2026</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="4">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="16"/>
-      <color theme="1"/>
       <name val="Arial Narrow"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="16"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Arial Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Arial Narrow"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -107,7 +59,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -198,69 +150,139 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="20">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -560,310 +582,334 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9048985C-5EC9-4547-A24A-B892F22ACCBA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A2:I25"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.5"/>
   <cols>
-    <col min="1" max="1" width="5.08203125" customWidth="1"/>
-    <col min="2" max="2" width="20.58203125" customWidth="1"/>
-    <col min="3" max="3" width="33.58203125" customWidth="1"/>
-    <col min="4" max="4" width="13.83203125" style="9" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="70.83203125" customWidth="1"/>
-    <col min="6" max="6" width="32.83203125" customWidth="1"/>
-    <col min="7" max="7" width="18.08203125" style="9" customWidth="1"/>
-    <col min="8" max="8" width="21.6640625" style="9" customWidth="1"/>
-    <col min="9" max="9" width="9.25" customWidth="1"/>
+    <col width="5.08203125" customWidth="1" min="1" max="1"/>
+    <col width="20.58203125" customWidth="1" min="2" max="2"/>
+    <col width="33.58203125" customWidth="1" min="3" max="3"/>
+    <col hidden="1" width="13.83203125" customWidth="1" style="9" min="4" max="4"/>
+    <col width="70.83203125" customWidth="1" min="5" max="5"/>
+    <col width="32.83203125" customWidth="1" min="6" max="6"/>
+    <col width="18.08203125" customWidth="1" style="9" min="7" max="7"/>
+    <col width="21.6640625" customWidth="1" style="9" min="8" max="8"/>
+    <col width="9.25" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" ht="20" x14ac:dyDescent="0.35">
-      <c r="A2" s="15" t="s">
-        <v>9</v>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>LAPORAN HASIL PENILAIAN KINERJA (SKP) ASN JULI TAHUN 2026</t>
+        </is>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="17"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" s="1"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="1"/>
-    </row>
-    <row r="4" spans="1:9" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
-        <v>0</v>
+      <c r="B2" s="18" t="n"/>
+      <c r="C2" s="18" t="n"/>
+      <c r="D2" s="18" t="n"/>
+      <c r="E2" s="18" t="n"/>
+      <c r="F2" s="18" t="n"/>
+      <c r="G2" s="18" t="n"/>
+      <c r="H2" s="18" t="n"/>
+      <c r="I2" s="19" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="n"/>
+      <c r="I3" s="1" t="n"/>
+    </row>
+    <row r="4" ht="37.5" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>1</v>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>NIP</t>
+        </is>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>2</v>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>NAMA</t>
+        </is>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>3</v>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>GOL. RUANG</t>
+        </is>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>4</v>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>JABATAN</t>
+        </is>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>5</v>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>UNIT KERJA</t>
+        </is>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>6</v>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>JENIS ASN</t>
+        </is>
       </c>
-      <c r="H4" s="5" t="s">
-        <v>7</v>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>NILAI SKP</t>
+        </is>
       </c>
-      <c r="I4" s="5" t="s">
-        <v>8</v>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>KET</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5" s="14"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="10"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A6" s="14"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="10"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7" s="14"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="10"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" s="14"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="10"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="14"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="10"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A10" s="14"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="10"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" s="14"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="10"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" s="14"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="10"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" s="14"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="10"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A14" s="14"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="10"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A15" s="14"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="10"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A16" s="14"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="10"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A17" s="14"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="10"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A18" s="14"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="10"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A19" s="14"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="10"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A20" s="14"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="10"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A21" s="14"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="10"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A22" s="14"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="10"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A23" s="14"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="10"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A24" s="14"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="10"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A25" s="14"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="10"/>
+    <row r="5">
+      <c r="A5" s="14" t="n"/>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="12" t="n"/>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="10" t="n"/>
+      <c r="G5" s="8" t="n"/>
+      <c r="H5" s="8" t="n"/>
+      <c r="I5" s="10" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="n"/>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="10" t="n"/>
+      <c r="G6" s="8" t="n"/>
+      <c r="H6" s="8" t="n"/>
+      <c r="I6" s="10" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="n"/>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="12" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="10" t="n"/>
+      <c r="G7" s="8" t="n"/>
+      <c r="H7" s="8" t="n"/>
+      <c r="I7" s="10" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="n"/>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="12" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="10" t="n"/>
+      <c r="G8" s="8" t="n"/>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="10" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="n"/>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="12" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="8" t="n"/>
+      <c r="H9" s="8" t="n"/>
+      <c r="I9" s="10" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="n"/>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="12" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="10" t="n"/>
+      <c r="G10" s="8" t="n"/>
+      <c r="H10" s="8" t="n"/>
+      <c r="I10" s="10" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="n"/>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="12" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="10" t="n"/>
+      <c r="G11" s="8" t="n"/>
+      <c r="H11" s="8" t="n"/>
+      <c r="I11" s="10" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="12" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="10" t="n"/>
+      <c r="G12" s="8" t="n"/>
+      <c r="H12" s="8" t="n"/>
+      <c r="I12" s="10" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="n"/>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="13" t="n"/>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="10" t="n"/>
+      <c r="G13" s="11" t="n"/>
+      <c r="H13" s="8" t="n"/>
+      <c r="I13" s="10" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="n"/>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="13" t="n"/>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="10" t="n"/>
+      <c r="G14" s="11" t="n"/>
+      <c r="H14" s="8" t="n"/>
+      <c r="I14" s="10" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="n"/>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="13" t="n"/>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="10" t="n"/>
+      <c r="G15" s="11" t="n"/>
+      <c r="H15" s="8" t="n"/>
+      <c r="I15" s="10" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="n"/>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="13" t="n"/>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="10" t="n"/>
+      <c r="G16" s="11" t="n"/>
+      <c r="H16" s="8" t="n"/>
+      <c r="I16" s="10" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="n"/>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="13" t="n"/>
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="10" t="n"/>
+      <c r="G17" s="11" t="n"/>
+      <c r="H17" s="8" t="n"/>
+      <c r="I17" s="10" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="n"/>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="12" t="n"/>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="10" t="n"/>
+      <c r="G18" s="8" t="n"/>
+      <c r="H18" s="8" t="n"/>
+      <c r="I18" s="10" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="n"/>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="12" t="n"/>
+      <c r="E19" s="7" t="n"/>
+      <c r="F19" s="10" t="n"/>
+      <c r="G19" s="8" t="n"/>
+      <c r="H19" s="8" t="n"/>
+      <c r="I19" s="10" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="n"/>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="12" t="n"/>
+      <c r="E20" s="7" t="n"/>
+      <c r="F20" s="10" t="n"/>
+      <c r="G20" s="8" t="n"/>
+      <c r="H20" s="8" t="n"/>
+      <c r="I20" s="10" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="n"/>
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="12" t="n"/>
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="10" t="n"/>
+      <c r="G21" s="8" t="n"/>
+      <c r="H21" s="8" t="n"/>
+      <c r="I21" s="10" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="n"/>
+      <c r="B22" s="7" t="n"/>
+      <c r="C22" s="7" t="n"/>
+      <c r="D22" s="12" t="n"/>
+      <c r="E22" s="7" t="n"/>
+      <c r="F22" s="10" t="n"/>
+      <c r="G22" s="8" t="n"/>
+      <c r="H22" s="8" t="n"/>
+      <c r="I22" s="10" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="n"/>
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="12" t="n"/>
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="10" t="n"/>
+      <c r="G23" s="8" t="n"/>
+      <c r="H23" s="8" t="n"/>
+      <c r="I23" s="10" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="n"/>
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="7" t="n"/>
+      <c r="D24" s="12" t="n"/>
+      <c r="E24" s="7" t="n"/>
+      <c r="F24" s="10" t="n"/>
+      <c r="G24" s="8" t="n"/>
+      <c r="H24" s="8" t="n"/>
+      <c r="I24" s="10" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="n"/>
+      <c r="B25" s="7" t="n"/>
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="7" t="n"/>
+      <c r="F25" s="10" t="n"/>
+      <c r="G25" s="8" t="n"/>
+      <c r="H25" s="8" t="n"/>
+      <c r="I25" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
--- a/Format Rekap SKP per OPD.xlsx
+++ b/Format Rekap SKP per OPD.xlsx
@@ -655,7 +655,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>UNIT KERJA</t>
+          <t>SATUAN KERJA</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">

--- a/Format Rekap SKP per OPD.xlsx
+++ b/Format Rekap SKP per OPD.xlsx
@@ -655,7 +655,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>SATUAN KERJA</t>
+          <t>UNIT KERJA</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
